--- a/artfynd/A 2437-2026 artfynd.xlsx
+++ b/artfynd/A 2437-2026 artfynd.xlsx
@@ -1041,7 +1041,7 @@
         <v>132176087</v>
       </c>
       <c r="B5" t="n">
-        <v>96325</v>
+        <v>96328</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>132176876</v>
       </c>
       <c r="B6" t="n">
-        <v>96325</v>
+        <v>96328</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>132179714</v>
       </c>
       <c r="B7" t="n">
-        <v>97960</v>
+        <v>97963</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 2437-2026 artfynd.xlsx
+++ b/artfynd/A 2437-2026 artfynd.xlsx
@@ -1252,45 +1252,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132179714</v>
+        <v>132177020</v>
       </c>
       <c r="B7" t="n">
-        <v>97963</v>
+        <v>57945</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lilla Mörtevattnet, Lilla Mörtevattnet, Boh</t>
+          <t>Kasen, Kasen, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>327021</v>
+        <v>327126</v>
       </c>
       <c r="R7" t="n">
-        <v>6457890</v>
+        <v>6458104</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,45 +1359,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132177020</v>
+        <v>132179714</v>
       </c>
       <c r="B8" t="n">
-        <v>57945</v>
+        <v>97963</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kasen, Kasen, Boh</t>
+          <t>Lilla Mörtevattnet, Lilla Mörtevattnet, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>327126</v>
+        <v>327021</v>
       </c>
       <c r="R8" t="n">
-        <v>6458104</v>
+        <v>6457890</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 2437-2026 artfynd.xlsx
+++ b/artfynd/A 2437-2026 artfynd.xlsx
@@ -1252,45 +1252,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132177020</v>
+        <v>132179714</v>
       </c>
       <c r="B7" t="n">
-        <v>57945</v>
+        <v>97963</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kasen, Kasen, Boh</t>
+          <t>Lilla Mörtevattnet, Lilla Mörtevattnet, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>327126</v>
+        <v>327021</v>
       </c>
       <c r="R7" t="n">
-        <v>6458104</v>
+        <v>6457890</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,45 +1359,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132179714</v>
+        <v>132177020</v>
       </c>
       <c r="B8" t="n">
-        <v>97963</v>
+        <v>57945</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lilla Mörtevattnet, Lilla Mörtevattnet, Boh</t>
+          <t>Kasen, Kasen, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>327021</v>
+        <v>327126</v>
       </c>
       <c r="R8" t="n">
-        <v>6457890</v>
+        <v>6458104</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 2437-2026 artfynd.xlsx
+++ b/artfynd/A 2437-2026 artfynd.xlsx
@@ -1041,7 +1041,7 @@
         <v>132176087</v>
       </c>
       <c r="B5" t="n">
-        <v>96328</v>
+        <v>96336</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>132176876</v>
       </c>
       <c r="B6" t="n">
-        <v>96328</v>
+        <v>96336</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>132179714</v>
       </c>
       <c r="B7" t="n">
-        <v>97963</v>
+        <v>97971</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>132177020</v>
       </c>
       <c r="B8" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 2437-2026 artfynd.xlsx
+++ b/artfynd/A 2437-2026 artfynd.xlsx
@@ -1252,45 +1252,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132179714</v>
+        <v>132177020</v>
       </c>
       <c r="B7" t="n">
-        <v>97971</v>
+        <v>57946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lilla Mörtevattnet, Lilla Mörtevattnet, Boh</t>
+          <t>Kasen, Kasen, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>327021</v>
+        <v>327126</v>
       </c>
       <c r="R7" t="n">
-        <v>6457890</v>
+        <v>6458104</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,45 +1359,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132177020</v>
+        <v>132179714</v>
       </c>
       <c r="B8" t="n">
-        <v>57946</v>
+        <v>97971</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kasen, Kasen, Boh</t>
+          <t>Lilla Mörtevattnet, Lilla Mörtevattnet, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>327126</v>
+        <v>327021</v>
       </c>
       <c r="R8" t="n">
-        <v>6458104</v>
+        <v>6457890</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 2437-2026 artfynd.xlsx
+++ b/artfynd/A 2437-2026 artfynd.xlsx
@@ -1041,7 +1041,7 @@
         <v>132176087</v>
       </c>
       <c r="B5" t="n">
-        <v>96336</v>
+        <v>96346</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>132176876</v>
       </c>
       <c r="B6" t="n">
-        <v>96336</v>
+        <v>96346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,45 +1252,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132177020</v>
+        <v>132179714</v>
       </c>
       <c r="B7" t="n">
-        <v>57946</v>
+        <v>97981</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kasen, Kasen, Boh</t>
+          <t>Lilla Mörtevattnet, Lilla Mörtevattnet, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>327126</v>
+        <v>327021</v>
       </c>
       <c r="R7" t="n">
-        <v>6458104</v>
+        <v>6457890</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,45 +1359,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132179714</v>
+        <v>132177020</v>
       </c>
       <c r="B8" t="n">
-        <v>97971</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lilla Mörtevattnet, Lilla Mörtevattnet, Boh</t>
+          <t>Kasen, Kasen, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>327021</v>
+        <v>327126</v>
       </c>
       <c r="R8" t="n">
-        <v>6457890</v>
+        <v>6458104</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 2437-2026 artfynd.xlsx
+++ b/artfynd/A 2437-2026 artfynd.xlsx
@@ -1041,7 +1041,7 @@
         <v>132176087</v>
       </c>
       <c r="B5" t="n">
-        <v>96346</v>
+        <v>96348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>132176876</v>
       </c>
       <c r="B6" t="n">
-        <v>96346</v>
+        <v>96348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,45 +1252,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132179714</v>
+        <v>132177020</v>
       </c>
       <c r="B7" t="n">
-        <v>97981</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lilla Mörtevattnet, Lilla Mörtevattnet, Boh</t>
+          <t>Kasen, Kasen, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>327021</v>
+        <v>327126</v>
       </c>
       <c r="R7" t="n">
-        <v>6457890</v>
+        <v>6458104</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,45 +1359,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132177020</v>
+        <v>132179714</v>
       </c>
       <c r="B8" t="n">
-        <v>57950</v>
+        <v>97983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kasen, Kasen, Boh</t>
+          <t>Lilla Mörtevattnet, Lilla Mörtevattnet, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>327126</v>
+        <v>327021</v>
       </c>
       <c r="R8" t="n">
-        <v>6458104</v>
+        <v>6457890</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 2437-2026 artfynd.xlsx
+++ b/artfynd/A 2437-2026 artfynd.xlsx
@@ -1252,45 +1252,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132177020</v>
+        <v>132179714</v>
       </c>
       <c r="B7" t="n">
-        <v>57950</v>
+        <v>97983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kasen, Kasen, Boh</t>
+          <t>Lilla Mörtevattnet, Lilla Mörtevattnet, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>327126</v>
+        <v>327021</v>
       </c>
       <c r="R7" t="n">
-        <v>6458104</v>
+        <v>6457890</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,45 +1359,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132179714</v>
+        <v>132177020</v>
       </c>
       <c r="B8" t="n">
-        <v>97983</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lilla Mörtevattnet, Lilla Mörtevattnet, Boh</t>
+          <t>Kasen, Kasen, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>327021</v>
+        <v>327126</v>
       </c>
       <c r="R8" t="n">
-        <v>6457890</v>
+        <v>6458104</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 2437-2026 artfynd.xlsx
+++ b/artfynd/A 2437-2026 artfynd.xlsx
@@ -1041,7 +1041,7 @@
         <v>132176087</v>
       </c>
       <c r="B5" t="n">
-        <v>96348</v>
+        <v>96349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>132176876</v>
       </c>
       <c r="B6" t="n">
-        <v>96348</v>
+        <v>96349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>132179714</v>
       </c>
       <c r="B7" t="n">
-        <v>97983</v>
+        <v>97984</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>132177020</v>
       </c>
       <c r="B8" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 2437-2026 artfynd.xlsx
+++ b/artfynd/A 2437-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105622787</v>
+        <v>132176087</v>
       </c>
       <c r="B2" t="n">
-        <v>108194</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96423</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219711</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>HJÄRTUM: LILLA MÖRTEVATTNET, V OM, Boh</t>
+          <t>Kasen, Kasen, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>326894.4381839141</v>
+        <v>327191</v>
       </c>
       <c r="R2" t="n">
-        <v>6457889.931074166</v>
+        <v>6458131</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1920-01-01</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1945-12-31</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Lokaluppgifter från H. Fries 1945 Göteborgs och Bohusläns fanerogamer och ormbunkar - sammanställt av Alistair Auffret för historiska analyser av förändring i utbredningar</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,31 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Mora Aronsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Göteborg och Bohusläns flora 1945</t>
-        </is>
-      </c>
+          <t>Anna Zeffer</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105622790</v>
+        <v>132176876</v>
       </c>
       <c r="B3" t="n">
-        <v>104490</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96423</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219686</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>HJÄRTUM: LILLA MÖRTEVATTNET, BÄCK SO OM, Boh</t>
+          <t>Kasen, Kasen, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>326894.2786865123</v>
+        <v>327172</v>
       </c>
       <c r="R3" t="n">
-        <v>6457789.745844994</v>
+        <v>6458060</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,27 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1920-01-01</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1945-12-31</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Lokaluppgifter från H. Fries 1945 Göteborgs och Bohusläns fanerogamer och ormbunkar - sammanställt av Alistair Auffret för historiska analyser av förändring i utbredningar</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,31 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Mora Aronsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Göteborg och Bohusläns flora 1945</t>
-        </is>
-      </c>
+          <t>Anna Zeffer</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105622791</v>
+        <v>132177020</v>
       </c>
       <c r="B4" t="n">
-        <v>108194</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,37 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>HJÄRTUM: LILLA MÖRTEVATTNET, BÄCK SO OM, Boh</t>
+          <t>Kasen, Kasen, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>326894.2786865123</v>
+        <v>327126</v>
       </c>
       <c r="R4" t="n">
-        <v>6457789.745844994</v>
+        <v>6458104</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,27 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1920-01-01</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1945-12-31</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Lokaluppgifter från H. Fries 1945 Göteborgs och Bohusläns fanerogamer och ormbunkar - sammanställt av Alistair Auffret för historiska analyser av förändring i utbredningar</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,48 +984,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Mora Aronsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Göteborg och Bohusläns flora 1945</t>
-        </is>
-      </c>
+          <t>Anna Zeffer</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132176087</v>
+        <v>132177957</v>
       </c>
       <c r="B5" t="n">
-        <v>96352</v>
+        <v>56706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>206046</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1073,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>327191</v>
+        <v>327109</v>
       </c>
       <c r="R5" t="n">
-        <v>6458131</v>
+        <v>6458037</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1118,7 +1076,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färsk spillning</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132176876</v>
+        <v>105622790</v>
       </c>
       <c r="B6" t="n">
-        <v>96352</v>
+        <v>107609</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1156,37 +1119,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2810</v>
+        <v>219686</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kasen, Kasen, Boh</t>
+          <t>HJÄRTUM: LILLA MÖRTEVATTNET, BÄCK SO OM, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>327172</v>
+        <v>326895</v>
       </c>
       <c r="R6" t="n">
-        <v>6458060</v>
+        <v>6457790</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,22 +1173,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:44</t>
+          <t>1920-01-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:44</t>
+          <t>1945-12-31</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Lokaluppgifter från H. Fries 1945 Göteborgs och Bohusläns fanerogamer och ormbunkar - sammanställt av Alistair Auffret för historiska analyser av förändring i utbredningar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,22 +1198,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Via Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Göteborg och Bohusläns flora 1945</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132177020</v>
+        <v>105622787</v>
       </c>
       <c r="B7" t="n">
-        <v>57951</v>
+        <v>111390</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1263,37 +1225,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kasen, Kasen, Boh</t>
+          <t>HJÄRTUM: LILLA MÖRTEVATTNET, V OM, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>327126</v>
+        <v>326894</v>
       </c>
       <c r="R7" t="n">
-        <v>6458104</v>
+        <v>6457890</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1317,22 +1279,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:51</t>
+          <t>1920-01-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:51</t>
+          <t>1945-12-31</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Lokaluppgifter från H. Fries 1945 Göteborgs och Bohusläns fanerogamer och ormbunkar - sammanställt av Alistair Auffret för historiska analyser av förändring i utbredningar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,39 +1304,43 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Via Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Göteborg och Bohusläns flora 1945</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132179714</v>
+        <v>105622791</v>
       </c>
       <c r="B8" t="n">
-        <v>97987</v>
+        <v>111390</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>219711</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1390,17 +1351,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lilla Mörtevattnet, Lilla Mörtevattnet, Boh</t>
+          <t>HJÄRTUM: LILLA MÖRTEVATTNET, BÄCK SO OM, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>327021</v>
+        <v>326895</v>
       </c>
       <c r="R8" t="n">
-        <v>6457890</v>
+        <v>6457790</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1424,22 +1385,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:15</t>
+          <t>1920-01-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:15</t>
+          <t>1945-12-31</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Lokaluppgifter från H. Fries 1945 Göteborgs och Bohusläns fanerogamer och ormbunkar - sammanställt av Alistair Auffret för historiska analyser av förändring i utbredningar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,15 +1410,233 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Göteborg och Bohusläns flora 1945</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132178238</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kasen, Kasen, Boh</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>327102</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6458059</v>
+      </c>
+      <c r="S9" t="n">
+        <v>13</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Anna Zeffer</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Anna Zeffer</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132179714</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lilla Mörtevattnet, Lilla Mörtevattnet, Boh</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>327021</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6457890</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anna Zeffer</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anna Zeffer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2437-2026 artfynd.xlsx
+++ b/artfynd/A 2437-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132176087</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132176876</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132177020</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132177957</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
           <t>Göteborg och Bohusläns flora 1945</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105622790</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1317,6 +1347,11 @@
           <t>Göteborg och Bohusläns flora 1945</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105622787</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1423,6 +1458,11 @@
           <t>Göteborg och Bohusläns flora 1945</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105622791</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1530,6 +1570,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132178238</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1637,8 +1682,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132179714</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>